--- a/app/src/main/java/com/example/methodmesh/modules/weather/docs/example_odk_showcase_weather_radar.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/weather/docs/example_odk_showcase_weather_radar.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R2b9734272a3b49b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" r:id="Rdcd1f2ba05e444ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="3" r:id="R8adec3ad4f4b455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R52275c3f95fd4833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" r:id="R9e536b86743d46b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="3" r:id="R31374fe79fd94c79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,15 +319,15 @@
       <x:c r="C2" s="10" t="str">
         <x:v>Latitude</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str"/>
+      <x:c r="D2" s="10"/>
       <x:c r="E2" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str"/>
+      <x:c r="F2" s="10"/>
       <x:c r="G2" s="10" t="str">
         <x:v>51.5074</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str"/>
+      <x:c r="H2" s="10"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
@@ -339,15 +339,15 @@
       <x:c r="C3" s="10" t="str">
         <x:v>Longitude</x:v>
       </x:c>
-      <x:c r="D3" s="10" t="str"/>
+      <x:c r="D3" s="10"/>
       <x:c r="E3" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F3" s="10" t="str"/>
+      <x:c r="F3" s="10"/>
       <x:c r="G3" s="10" t="str">
         <x:v>-0.1278</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str"/>
+      <x:c r="H3" s="10"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
@@ -359,11 +359,11 @@
       <x:c r="C4" s="10" t="str">
         <x:v>Radar frame time (ISO-8601 UTC, optional)</x:v>
       </x:c>
-      <x:c r="D4" s="10" t="str"/>
-      <x:c r="E4" s="10" t="str"/>
-      <x:c r="F4" s="10" t="str"/>
-      <x:c r="G4" s="10" t="str"/>
-      <x:c r="H4" s="10" t="str"/>
+      <x:c r="D4" s="10"/>
+      <x:c r="E4" s="10"/>
+      <x:c r="F4" s="10"/>
+      <x:c r="G4" s="10"/>
+      <x:c r="H4" s="10"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
@@ -375,13 +375,13 @@
       <x:c r="C5" s="10" t="str">
         <x:v>Initial radar zoom (1–7)</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="str"/>
-      <x:c r="E5" s="10" t="str"/>
-      <x:c r="F5" s="10" t="str"/>
+      <x:c r="D5" s="10"/>
+      <x:c r="E5" s="10"/>
+      <x:c r="F5" s="10"/>
       <x:c r="G5" s="10" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="10"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
@@ -393,13 +393,13 @@
       <x:c r="C6" s="10" t="str">
         <x:v>Use cache only</x:v>
       </x:c>
-      <x:c r="D6" s="10" t="str"/>
-      <x:c r="E6" s="10" t="str"/>
-      <x:c r="F6" s="10" t="str"/>
+      <x:c r="D6" s="10"/>
+      <x:c r="E6" s="10"/>
+      <x:c r="F6" s="10"/>
       <x:c r="G6" s="10" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str"/>
+      <x:c r="H6" s="10"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
@@ -414,9 +414,9 @@
       <x:c r="D7" s="10" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="str"/>
-      <x:c r="F7" s="10" t="str"/>
-      <x:c r="G7" s="10" t="str"/>
+      <x:c r="E7" s="10"/>
+      <x:c r="F7" s="10"/>
+      <x:c r="G7" s="10"/>
       <x:c r="H7" s="10" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='weather.radar',input_latitude=${req_latitude},input_longitude=${req_longitude},input_frame_time_iso=${req_frame_time_iso},input_zoom=${req_zoom},input_offline_only=${req_offline_only},input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
@@ -431,13 +431,13 @@
       <x:c r="C8" s="10" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="D8" s="10" t="str"/>
-      <x:c r="E8" s="10" t="str"/>
+      <x:c r="D8" s="10"/>
+      <x:c r="E8" s="10"/>
       <x:c r="F8" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str"/>
-      <x:c r="H8" s="10" t="str"/>
+      <x:c r="G8" s="10"/>
+      <x:c r="H8" s="10"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
@@ -449,13 +449,13 @@
       <x:c r="C9" s="10" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="D9" s="10" t="str"/>
-      <x:c r="E9" s="10" t="str"/>
+      <x:c r="D9" s="10"/>
+      <x:c r="E9" s="10"/>
       <x:c r="F9" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="str"/>
-      <x:c r="H9" s="10" t="str"/>
+      <x:c r="G9" s="10"/>
+      <x:c r="H9" s="10"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
@@ -467,13 +467,13 @@
       <x:c r="C10" s="10" t="str">
         <x:v>Requested latitude</x:v>
       </x:c>
-      <x:c r="D10" s="10" t="str"/>
-      <x:c r="E10" s="10" t="str"/>
+      <x:c r="D10" s="10"/>
+      <x:c r="E10" s="10"/>
       <x:c r="F10" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str"/>
-      <x:c r="H10" s="10" t="str"/>
+      <x:c r="G10" s="10"/>
+      <x:c r="H10" s="10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10" t="str">
@@ -485,13 +485,13 @@
       <x:c r="C11" s="10" t="str">
         <x:v>Requested longitude</x:v>
       </x:c>
-      <x:c r="D11" s="10" t="str"/>
-      <x:c r="E11" s="10" t="str"/>
+      <x:c r="D11" s="10"/>
+      <x:c r="E11" s="10"/>
       <x:c r="F11" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="str"/>
-      <x:c r="H11" s="10" t="str"/>
+      <x:c r="G11" s="10"/>
+      <x:c r="H11" s="10"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
@@ -503,13 +503,13 @@
       <x:c r="C12" s="10" t="str">
         <x:v>Frame time ISO</x:v>
       </x:c>
-      <x:c r="D12" s="10" t="str"/>
-      <x:c r="E12" s="10" t="str"/>
+      <x:c r="D12" s="10"/>
+      <x:c r="E12" s="10"/>
       <x:c r="F12" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str"/>
-      <x:c r="H12" s="10" t="str"/>
+      <x:c r="G12" s="10"/>
+      <x:c r="H12" s="10"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10" t="str">
@@ -521,13 +521,13 @@
       <x:c r="C13" s="10" t="str">
         <x:v>Frame class</x:v>
       </x:c>
-      <x:c r="D13" s="10" t="str"/>
-      <x:c r="E13" s="10" t="str"/>
+      <x:c r="D13" s="10"/>
+      <x:c r="E13" s="10"/>
       <x:c r="F13" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="str"/>
-      <x:c r="H13" s="10" t="str"/>
+      <x:c r="G13" s="10"/>
+      <x:c r="H13" s="10"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
@@ -539,13 +539,13 @@
       <x:c r="C14" s="10" t="str">
         <x:v>Provider</x:v>
       </x:c>
-      <x:c r="D14" s="10" t="str"/>
-      <x:c r="E14" s="10" t="str"/>
+      <x:c r="D14" s="10"/>
+      <x:c r="E14" s="10"/>
       <x:c r="F14" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G14" s="10" t="str"/>
-      <x:c r="H14" s="10" t="str"/>
+      <x:c r="G14" s="10"/>
+      <x:c r="H14" s="10"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="10" t="str">
@@ -557,13 +557,13 @@
       <x:c r="C15" s="10" t="str">
         <x:v>Coverage state</x:v>
       </x:c>
-      <x:c r="D15" s="10" t="str"/>
-      <x:c r="E15" s="10" t="str"/>
+      <x:c r="D15" s="10"/>
+      <x:c r="E15" s="10"/>
       <x:c r="F15" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G15" s="10" t="str"/>
-      <x:c r="H15" s="10" t="str"/>
+      <x:c r="G15" s="10"/>
+      <x:c r="H15" s="10"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="10" t="str">
@@ -575,13 +575,13 @@
       <x:c r="C16" s="10" t="str">
         <x:v>Host</x:v>
       </x:c>
-      <x:c r="D16" s="10" t="str"/>
-      <x:c r="E16" s="10" t="str"/>
+      <x:c r="D16" s="10"/>
+      <x:c r="E16" s="10"/>
       <x:c r="F16" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G16" s="10" t="str"/>
-      <x:c r="H16" s="10" t="str"/>
+      <x:c r="G16" s="10"/>
+      <x:c r="H16" s="10"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="10" t="str">
@@ -593,13 +593,13 @@
       <x:c r="C17" s="10" t="str">
         <x:v>Frame path</x:v>
       </x:c>
-      <x:c r="D17" s="10" t="str"/>
-      <x:c r="E17" s="10" t="str"/>
+      <x:c r="D17" s="10"/>
+      <x:c r="E17" s="10"/>
       <x:c r="F17" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G17" s="10" t="str"/>
-      <x:c r="H17" s="10" t="str"/>
+      <x:c r="G17" s="10"/>
+      <x:c r="H17" s="10"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="10" t="str">
@@ -611,13 +611,13 @@
       <x:c r="C18" s="10" t="str">
         <x:v>Tile template</x:v>
       </x:c>
-      <x:c r="D18" s="10" t="str"/>
-      <x:c r="E18" s="10" t="str"/>
+      <x:c r="D18" s="10"/>
+      <x:c r="E18" s="10"/>
       <x:c r="F18" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G18" s="10" t="str"/>
-      <x:c r="H18" s="10" t="str"/>
+      <x:c r="G18" s="10"/>
+      <x:c r="H18" s="10"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
@@ -629,13 +629,13 @@
       <x:c r="C19" s="10" t="str">
         <x:v>Zoom</x:v>
       </x:c>
-      <x:c r="D19" s="10" t="str"/>
-      <x:c r="E19" s="10" t="str"/>
+      <x:c r="D19" s="10"/>
+      <x:c r="E19" s="10"/>
       <x:c r="F19" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G19" s="10" t="str"/>
-      <x:c r="H19" s="10" t="str"/>
+      <x:c r="G19" s="10"/>
+      <x:c r="H19" s="10"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
@@ -647,13 +647,13 @@
       <x:c r="C20" s="10" t="str">
         <x:v>Observed frame count</x:v>
       </x:c>
-      <x:c r="D20" s="10" t="str"/>
-      <x:c r="E20" s="10" t="str"/>
+      <x:c r="D20" s="10"/>
+      <x:c r="E20" s="10"/>
       <x:c r="F20" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G20" s="10" t="str"/>
-      <x:c r="H20" s="10" t="str"/>
+      <x:c r="G20" s="10"/>
+      <x:c r="H20" s="10"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10" t="str">
@@ -665,13 +665,13 @@
       <x:c r="C21" s="10" t="str">
         <x:v>Nowcast frame count</x:v>
       </x:c>
-      <x:c r="D21" s="10" t="str"/>
-      <x:c r="E21" s="10" t="str"/>
+      <x:c r="D21" s="10"/>
+      <x:c r="E21" s="10"/>
       <x:c r="F21" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G21" s="10" t="str"/>
-      <x:c r="H21" s="10" t="str"/>
+      <x:c r="G21" s="10"/>
+      <x:c r="H21" s="10"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="10" t="str">
@@ -686,156 +686,192 @@
       <x:c r="D22" s="10" t="str">
         <x:v>multiline</x:v>
       </x:c>
-      <x:c r="E22" s="10" t="str"/>
+      <x:c r="E22" s="10"/>
       <x:c r="F22" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G22" s="10" t="str"/>
-      <x:c r="H22" s="10" t="str"/>
+      <x:c r="G22" s="10"/>
+      <x:c r="H22" s="10"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="10" t="str">
-        <x:v>text</x:v>
+        <x:v>image</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>weather_radar_retrieved_time_iso</x:v>
+        <x:v>weather_radar_gif_uri</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>Retrieved time ISO</x:v>
-      </x:c>
-      <x:c r="D23" s="10" t="str"/>
-      <x:c r="E23" s="10" t="str"/>
+        <x:v>Radar animation (GIF)</x:v>
+      </x:c>
+      <x:c r="D23" s="10"/>
+      <x:c r="E23" s="10"/>
       <x:c r="F23" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G23" s="10" t="str"/>
-      <x:c r="H23" s="10" t="str"/>
+      <x:c r="G23" s="10"/>
+      <x:c r="H23" s="10"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>weather_radar_from_cache</x:v>
+        <x:v>weather_radar_gif_sha256</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>From cache</x:v>
-      </x:c>
-      <x:c r="D24" s="10" t="str"/>
-      <x:c r="E24" s="10" t="str"/>
+        <x:v>Radar GIF SHA-256</x:v>
+      </x:c>
+      <x:c r="D24" s="10"/>
+      <x:c r="E24" s="10"/>
       <x:c r="F24" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G24" s="10" t="str"/>
-      <x:c r="H24" s="10" t="str"/>
+      <x:c r="G24" s="10"/>
+      <x:c r="H24" s="10"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="10" t="str">
-        <x:v>decimal</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>weather_radar_data_age_hours</x:v>
+        <x:v>weather_radar_retrieved_time_iso</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>Data age hours</x:v>
-      </x:c>
-      <x:c r="D25" s="10" t="str"/>
-      <x:c r="E25" s="10" t="str"/>
+        <x:v>Retrieved time ISO</x:v>
+      </x:c>
+      <x:c r="D25" s="10"/>
+      <x:c r="E25" s="10"/>
       <x:c r="F25" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G25" s="10" t="str"/>
-      <x:c r="H25" s="10" t="str"/>
+      <x:c r="G25" s="10"/>
+      <x:c r="H25" s="10"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="10" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>weather_radar_audit_json</x:v>
+        <x:v>weather_radar_from_cache</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>Audit JSON</x:v>
-      </x:c>
-      <x:c r="D26" s="10" t="str">
-        <x:v>multiline</x:v>
-      </x:c>
-      <x:c r="E26" s="10" t="str"/>
+        <x:v>From cache</x:v>
+      </x:c>
+      <x:c r="D26" s="10"/>
+      <x:c r="E26" s="10"/>
       <x:c r="F26" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G26" s="10" t="str"/>
-      <x:c r="H26" s="10" t="str"/>
+      <x:c r="G26" s="10"/>
+      <x:c r="H26" s="10"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="10" t="str">
-        <x:v>text</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>weather_radar_error</x:v>
+        <x:v>weather_radar_data_age_hours</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>Error</x:v>
-      </x:c>
-      <x:c r="D27" s="10" t="str">
-        <x:v>multiline</x:v>
-      </x:c>
-      <x:c r="E27" s="10" t="str"/>
+        <x:v>Data age hours</x:v>
+      </x:c>
+      <x:c r="D27" s="10"/>
+      <x:c r="E27" s="10"/>
       <x:c r="F27" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G27" s="10" t="str"/>
-      <x:c r="H27" s="10" t="str"/>
+      <x:c r="G27" s="10"/>
+      <x:c r="H27" s="10"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="10" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>methodmesh_status</x:v>
+        <x:v>weather_radar_audit_json</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>MethodMesh status</x:v>
-      </x:c>
-      <x:c r="D28" s="10" t="str"/>
-      <x:c r="E28" s="10" t="str"/>
+        <x:v>Audit JSON</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="str">
+        <x:v>multiline</x:v>
+      </x:c>
+      <x:c r="E28" s="10"/>
       <x:c r="F28" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G28" s="10" t="str"/>
-      <x:c r="H28" s="10" t="str"/>
+      <x:c r="G28" s="10"/>
+      <x:c r="H28" s="10"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>weather_radar_error</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>MethodMesh full JSON</x:v>
+        <x:v>Error</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
         <x:v>multiline</x:v>
       </x:c>
-      <x:c r="E29" s="10" t="str"/>
+      <x:c r="E29" s="10"/>
       <x:c r="F29" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G29" s="10" t="str"/>
-      <x:c r="H29" s="10" t="str"/>
+      <x:c r="G29" s="10"/>
+      <x:c r="H29" s="10"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>methodmesh_status</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>MethodMesh status</x:v>
+      </x:c>
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10"/>
+      <x:c r="F30" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G30" s="10"/>
+      <x:c r="H30" s="10"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>MethodMesh full JSON</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>multiline</x:v>
+      </x:c>
+      <x:c r="E31"/>
+      <x:c r="F31" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
         <x:v>end_group</x:v>
       </x:c>
-      <x:c r="B30" s="10" t="str"/>
-      <x:c r="C30" s="10" t="str"/>
-      <x:c r="D30" s="10" t="str"/>
-      <x:c r="E30" s="10" t="str"/>
-      <x:c r="F30" s="10" t="str"/>
-      <x:c r="G30" s="10" t="str"/>
-      <x:c r="H30" s="10" t="str"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -874,7 +910,7 @@
         <x:v>methodmesh_weather_radar</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026091002</x:v>
+        <x:v>2026092401</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>English (en)</x:v>
